--- a/golf_streamlit/data/turneringsinfo.xlsx
+++ b/golf_streamlit/data/turneringsinfo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c624kh1\Documents\My Projects\golf_streamlit V2\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c624kh1\Documents\My Projects\min_git\golf_streamlit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA92BCF3-2961-42CA-94D9-2CE3E348993D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE15E0BF-972E-43B4-87FC-A4C8BED9F10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="996" yWindow="2244" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>VO 24</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>Inne_ind</t>
+  </si>
+  <si>
+    <t>VO 26</t>
   </si>
 </sst>
 </file>
@@ -403,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -479,6 +482,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>202601</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
